--- a/outputs/sheets/goodnotes.xlsx
+++ b/outputs/sheets/goodnotes.xlsx
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr"/>

--- a/outputs/sheets/goodnotes.xlsx
+++ b/outputs/sheets/goodnotes.xlsx
@@ -949,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M13"/>
+  <dimension ref="A2:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="B9" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="B10" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="B11" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="B12" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="B13" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
